--- a/FINAL_SUBMISSION/09_交易记录与盈亏归因/09_交易日志与盈亏归因.xlsx
+++ b/FINAL_SUBMISSION/09_交易记录与盈亏归因/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -517,17 +517,17 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.616</v>
+        <v>4.641</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>259900</v>
+        <v>258900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1199698.4</v>
+        <v>1201554.9</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>D2026090401</t>
+          <t>D2026090701</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -539,17 +539,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -558,17 +558,17 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>58.24</v>
+        <v>27.87</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>20600</v>
+        <v>13500</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1199744</v>
+        <v>376245</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>D2026090403</t>
+          <t>D2026090801</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -580,39 +580,80 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>601318</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>21200</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1189744</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>D2026090703</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>紫金矿业</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>601899</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>买入</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>33.35</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>35900</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>1197265</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>D2026090402</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>36500</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1231875</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>D2026090702</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
@@ -629,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -685,43 +726,43 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>259900</v>
+        <v>258900</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4.616</v>
+        <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.616</v>
+        <v>4.624</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1199698</v>
+        <v>1197154</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>-4401</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.37%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>20600</v>
+        <v>13500</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>58.24</v>
+        <v>27.87</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>58.24</v>
+        <v>27.87</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1199744</v>
+        <v>376245</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -735,27 +776,54 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>21200</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1180840</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-8904</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-0.75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>紫金矿业</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>35900</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>33.35</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>33.35</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1197265</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
+      <c r="B5" s="2" t="n">
+        <v>36500</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1235890</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4015</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
         </is>
       </c>
     </row>
@@ -836,7 +904,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1403292.6</v>
+        <v>1000581.1</v>
       </c>
     </row>
     <row r="4">
@@ -846,7 +914,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3596707.4</v>
+        <v>3990128.6</v>
       </c>
     </row>
     <row r="5">
@@ -856,7 +924,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5000000</v>
+        <v>4990709.7</v>
       </c>
     </row>
     <row r="6">
@@ -867,7 +935,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.19%</t>
         </is>
       </c>
     </row>
@@ -878,7 +946,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>899.1799999999999</v>
+        <v>999.85</v>
       </c>
     </row>
   </sheetData>

--- a/FINAL_SUBMISSION/09_交易记录与盈亏归因/09_交易日志与盈亏归因.xlsx
+++ b/FINAL_SUBMISSION/09_交易记录与盈亏归因/09_交易日志与盈亏归因.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -544,12 +544,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -558,17 +558,17 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>27.87</v>
+        <v>56.12</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13500</v>
+        <v>21200</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>376245</v>
+        <v>1189744</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>D2026090801</t>
+          <t>D2026090703</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -599,17 +599,17 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>56.12</v>
+        <v>33.75</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>21200</v>
+        <v>36500</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1189744</v>
+        <v>1231875</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>D2026090703</t>
+          <t>D2026090702</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -621,41 +621,82 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>长江电力</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>600900</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>27.839</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>375826.5</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>D2026090801</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>紫金矿业</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>601899</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>36500</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1231875</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>D2026090702</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>auto</t>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>18200</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>616252</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>D20260909M01</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -732,98 +773,98 @@
         <v>4.641</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4.624</v>
+        <v>4.629</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1197154</v>
+        <v>1198448</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4401</v>
+        <v>-3107</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>13500</v>
+        <v>21200</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>27.87</v>
+        <v>56.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>27.87</v>
+        <v>56.42</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>376245</v>
+        <v>1196104</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>6360</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.53%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>21200</v>
+        <v>18300</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>56.12</v>
+        <v>33.75</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>55.7</v>
+        <v>34.01</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1180840</v>
+        <v>622383</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-8904</v>
+        <v>4758</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>+0.77%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>36500</v>
+        <v>13500</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>33.75</v>
+        <v>27.839</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>33.86</v>
+        <v>27.95</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1235890</v>
+        <v>377325</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4015</v>
+        <v>1499</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.40%</t>
         </is>
       </c>
     </row>
@@ -838,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -855,6 +896,16 @@
         <is>
           <t>已实现盈亏(元)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2002</v>
       </c>
     </row>
   </sheetData>
@@ -904,7 +955,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1000581.1</v>
+        <v>1617251.6</v>
       </c>
     </row>
     <row r="4">
@@ -914,7 +965,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3990128.6</v>
+        <v>3394260.1</v>
       </c>
     </row>
     <row r="5">
@@ -924,7 +975,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4990709.7</v>
+        <v>5011511.7</v>
       </c>
     </row>
     <row r="6">
@@ -935,7 +986,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.23%</t>
         </is>
       </c>
     </row>
@@ -946,7 +997,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>999.85</v>
+        <v>1461.94</v>
       </c>
     </row>
   </sheetData>
